--- a/plc_data.xlsx
+++ b/plc_data.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM TABLE" sheetId="1" r:id="Rfcfcb821a81948e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM TABLE" sheetId="1" r:id="R6f544c1846184f04"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/plc_data.xlsx
+++ b/plc_data.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM TABLE" sheetId="1" r:id="R6f544c1846184f04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM TABLE" sheetId="1" r:id="Re275918c5d8742d7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/plc_data.xlsx
+++ b/plc_data.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM TABLE" sheetId="1" r:id="Re275918c5d8742d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM TABLE" sheetId="1" r:id="Re29b9c718df04a8e"/>
   </x:sheets>
 </x:workbook>
 </file>
